--- a/Bank Customer Churn Prediction.xlsx
+++ b/Bank Customer Churn Prediction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MITS\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD8E71A7-3E2B-498C-AEBF-3FCCCBD400A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4931966E-6E27-4255-83F8-8823FB98435D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FF349FF-FCE3-4B3A-A4EA-CAABA5C13D87}"/>
   </bookViews>
@@ -740,7 +740,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
@@ -760,6 +760,8 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="8" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="11"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -807,6 +809,38 @@
   </cellStyles>
   <dxfs count="29">
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -820,10 +854,10 @@
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -835,22 +869,6 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <border outline="0">
         <top style="thin">
           <color indexed="64"/>
@@ -890,22 +908,6 @@
         </right>
         <top/>
         <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -1298,8 +1300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6EC8ECFA-0A23-4901-9A0F-0FBC221C2ACC}" name="Table1" displayName="Table1" ref="B4:N24" totalsRowShown="0" headerRowDxfId="12" headerRowBorderDxfId="27" tableBorderDxfId="28" totalsRowBorderDxfId="26">
-  <autoFilter ref="B4:N24" xr:uid="{6EC8ECFA-0A23-4901-9A0F-0FBC221C2ACC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6EC8ECFA-0A23-4901-9A0F-0FBC221C2ACC}" name="Table1" displayName="Table1" ref="B4:N28" totalsRowShown="0" headerRowDxfId="12" headerRowBorderDxfId="27" tableBorderDxfId="28" totalsRowBorderDxfId="26">
+  <autoFilter ref="B4:N28" xr:uid="{6EC8ECFA-0A23-4901-9A0F-0FBC221C2ACC}"/>
   <tableColumns count="13">
     <tableColumn id="18" xr3:uid="{127FA4E4-70B3-4233-A999-93914ECD649D}" name="SNO" dataDxfId="25"/>
     <tableColumn id="1" xr3:uid="{0A0F49BB-B1CC-490B-9D13-4067EB85FEF9}" name="customer_id" dataDxfId="24"/>
@@ -1320,22 +1322,22 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A3BC6043-276F-4F5C-B8E4-2DC5C7286C56}" name="Table3" displayName="Table3" ref="Q11:R20" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="10" tableBorderDxfId="11" totalsRowBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A3BC6043-276F-4F5C-B8E4-2DC5C7286C56}" name="Table3" displayName="Table3" ref="Q11:R20" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="10" tableBorderDxfId="11" totalsRowBorderDxfId="9">
   <autoFilter ref="Q11:R20" xr:uid="{A3BC6043-276F-4F5C-B8E4-2DC5C7286C56}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4C4E0D76-3A6C-46C6-8347-20299C4C2AE5}" name="Column1" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{32558020-49BC-4392-ABB4-BEA5E1517DB4}" name="Column2" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{32558020-49BC-4392-ABB4-BEA5E1517DB4}" name="Column2" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CBDFCA0C-783D-4187-9E88-F0673AE07535}" name="Table4" displayName="Table4" ref="U8:V23" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="4" tableBorderDxfId="5" totalsRowBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CBDFCA0C-783D-4187-9E88-F0673AE07535}" name="Table4" displayName="Table4" ref="U8:V23" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="5" tableBorderDxfId="6" totalsRowBorderDxfId="4">
   <autoFilter ref="U8:V23" xr:uid="{CBDFCA0C-783D-4187-9E88-F0673AE07535}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{3B2AC2AC-A32C-420A-AEFA-79223134FA2F}" name="Column1" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{FC160988-DE1C-48AA-9D31-12A8495C5D10}" name="Column2" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{3B2AC2AC-A32C-420A-AEFA-79223134FA2F}" name="Column1" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{FC160988-DE1C-48AA-9D31-12A8495C5D10}" name="Column2" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1937,7 +1939,7 @@
       <c r="U9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="V9" s="7">
+      <c r="V9" s="19">
         <f>AVERAGE(Table1[age])</f>
         <v>37.4</v>
       </c>
@@ -2046,7 +2048,7 @@
       <c r="U11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="V11" s="7">
+      <c r="V11" s="19">
         <f>MEDIAN(Table1[age])</f>
         <v>40</v>
       </c>
@@ -2100,7 +2102,7 @@
       <c r="Q12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="R12" s="7">
+      <c r="R12" s="19">
         <f>COUNT(B:B)</f>
         <v>22</v>
       </c>
@@ -2158,7 +2160,7 @@
       <c r="U13" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="V13" s="7">
+      <c r="V13" s="19">
         <f>MODE(Table1[age])</f>
         <v>24</v>
       </c>
@@ -2212,7 +2214,7 @@
       <c r="Q14" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="R14" s="7">
+      <c r="R14" s="19">
         <f>COUNTA(B:B)</f>
         <v>23</v>
       </c>
@@ -2270,7 +2272,7 @@
       <c r="U15" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="V15" s="7">
+      <c r="V15" s="19">
         <f>STDEV(Table1[balance])</f>
         <v>66022.171032270082</v>
       </c>
@@ -2324,7 +2326,7 @@
       <c r="Q16" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="R16" s="7">
+      <c r="R16" s="19">
         <f>COUNTBLANK(B5:B27)</f>
         <v>2</v>
       </c>
@@ -2376,7 +2378,7 @@
       <c r="U17" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="V17" s="7">
+      <c r="V17" s="19">
         <f>_xlfn.STDEV.S(Table1[balance])</f>
         <v>66022.171032270082</v>
       </c>
@@ -2431,7 +2433,7 @@
       <c r="Q18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="R18" s="7">
+      <c r="R18" s="19">
         <f>COUNTIF(Table1[age],"&gt;=40")</f>
         <v>10</v>
       </c>
@@ -2483,7 +2485,7 @@
       <c r="U19" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="V19" s="7">
+      <c r="V19" s="19">
         <f>CORREL(Table1[balance],Table1[estimated_salary])</f>
         <v>4.0797520847827465E-2</v>
       </c>
@@ -2531,7 +2533,7 @@
       <c r="Q20" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="R20" s="17">
+      <c r="R20" s="19">
         <f>COUNTIFS(Table1[SNO],"&gt;15",Table1[gender],"MALE")</f>
         <v>3</v>
       </c>
@@ -2581,7 +2583,7 @@
       <c r="U21" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="V21" s="7">
+      <c r="V21" s="19">
         <f>VAR(Table1[estimated_salary])</f>
         <v>2443829807.8799195</v>
       </c>
@@ -2672,7 +2674,7 @@
       <c r="U23" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="V23" s="17">
+      <c r="V23" s="19">
         <f>_xlfn.VAR.S(Table1[estimated_salary])</f>
         <v>2443829807.8799195</v>
       </c>
@@ -2718,15 +2720,69 @@
         <v>0</v>
       </c>
     </row>
+    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B25" s="5"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="7"/>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B26" s="5"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="7"/>
+    </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B27">
+      <c r="B27" s="5">
         <v>23</v>
       </c>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="7"/>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.25">
-      <c r="B28">
+      <c r="B28" s="18">
         <v>24</v>
       </c>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
